--- a/data/source/Synthetic_Dataset.xlsx
+++ b/data/source/Synthetic_Dataset.xlsx
@@ -20810,6 +20810,7 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{b1c9b508-7c6e-42bd-bedf-808292653d6c}" enabled="1" method="Standard" siteId="{2882be50-2012-4d88-ac86-544124e120c8}" contentBits="0" removed="0"/>
+  <clbl:label id="{3bc062e4-ac9d-4c17-b4dd-3aad637ff1ac}" enabled="0" method="" siteId="{3bc062e4-ac9d-4c17-b4dd-3aad637ff1ac}" removed="1"/>
+  <clbl:label id="{b1c9b508-7c6e-42bd-bedf-808292653d6c}" enabled="1" method="Standard" siteId="{2882be50-2012-4d88-ac86-544124e120c8}" removed="0"/>
 </clbl:labelList>
 </file>